--- a/cvsu_violation_balanced.xlsx
+++ b/cvsu_violation_balanced.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Harold Arevalo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92510500-5000-41A7-9438-9585114C6D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09895374-3BF6-4A91-A7D0-8E81C3829E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2853" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3090" uniqueCount="760">
   <si>
     <t>text</t>
   </si>
@@ -2063,6 +2063,243 @@
   </si>
   <si>
     <t>Isang mag-aaral ang gumamit ng internet sa kanyang cellphone upang hanapin ang tamang sagot habang nag-eexam. Ang ganitong gawain ay mahigpit na ipinagbabawal at itinuturing na cheating.</t>
+  </si>
+  <si>
+    <t>Dress code violation</t>
+  </si>
+  <si>
+    <t>Paglabag sa tamang uniform</t>
+  </si>
+  <si>
+    <t>Cheating incident</t>
+  </si>
+  <si>
+    <t>nangopya ng sagot</t>
+  </si>
+  <si>
+    <t>Pandaraya sa exam</t>
+  </si>
+  <si>
+    <t>brought liquor</t>
+  </si>
+  <si>
+    <t>Physical altercation</t>
+  </si>
+  <si>
+    <t>Pisikal na away</t>
+  </si>
+  <si>
+    <t>Bullying case</t>
+  </si>
+  <si>
+    <t>harassment a people or person</t>
+  </si>
+  <si>
+    <t>Improper attire</t>
+  </si>
+  <si>
+    <t>Hindi angkop na kasuotan</t>
+  </si>
+  <si>
+    <t>ID not worn</t>
+  </si>
+  <si>
+    <t>Hindi suot ang ID</t>
+  </si>
+  <si>
+    <t>Academic dishonesty</t>
+  </si>
+  <si>
+    <t>Di tapat sa akademikong gawain</t>
+  </si>
+  <si>
+    <t>Threatening behavior</t>
+  </si>
+  <si>
+    <t>Paninindak sa kaklase</t>
+  </si>
+  <si>
+    <t>pananakot sa kapwa studyante</t>
+  </si>
+  <si>
+    <t>pagbabanta sa mga tao sa paligid</t>
+  </si>
+  <si>
+    <t>Unauthorized entry</t>
+  </si>
+  <si>
+    <t>Bawal na pagpasok</t>
+  </si>
+  <si>
+    <t>Disruptive behavior</t>
+  </si>
+  <si>
+    <t>Nanggugulo sa klase</t>
+  </si>
+  <si>
+    <t>Use of foul language</t>
+  </si>
+  <si>
+    <t>Pagmumura sa campus</t>
+  </si>
+  <si>
+    <t>Plagiarism detected</t>
+  </si>
+  <si>
+    <t>Kinopyang gawa (plagiarism)</t>
+  </si>
+  <si>
+    <t>Verbal abuse</t>
+  </si>
+  <si>
+    <t>Pang-aabuso sa salita</t>
+  </si>
+  <si>
+    <t>Nagmumura sa school</t>
+  </si>
+  <si>
+    <t>minumura ang ibang tao tulad ng kaklase niya</t>
+  </si>
+  <si>
+    <t>No ID upon entry</t>
+  </si>
+  <si>
+    <t>ID not presented</t>
+  </si>
+  <si>
+    <t>No school ID</t>
+  </si>
+  <si>
+    <t>Unverified identity (no ID)</t>
+  </si>
+  <si>
+    <t>ID not visible</t>
+  </si>
+  <si>
+    <t>Improper ID display</t>
+  </si>
+  <si>
+    <t>Expired ID used</t>
+  </si>
+  <si>
+    <t>Borrowed ID</t>
+  </si>
+  <si>
+    <t>ID left at home</t>
+  </si>
+  <si>
+    <t>Hindi naipakitang ID</t>
+  </si>
+  <si>
+    <t>Walang dalang ID</t>
+  </si>
+  <si>
+    <t>Hindi ma-verify ang ID</t>
+  </si>
+  <si>
+    <t>Out of uniform</t>
+  </si>
+  <si>
+    <t>Incomplete uniform</t>
+  </si>
+  <si>
+    <t>Improper uniform</t>
+  </si>
+  <si>
+    <t>Dress code not followed</t>
+  </si>
+  <si>
+    <t>Wearing casual attire</t>
+  </si>
+  <si>
+    <t>Prohibited outfit</t>
+  </si>
+  <si>
+    <t>Non-compliant attire</t>
+  </si>
+  <si>
+    <t>Inappropriate clothing</t>
+  </si>
+  <si>
+    <t>Walang tamang uniporme</t>
+  </si>
+  <si>
+    <t>Hindi kumpletong uniporme</t>
+  </si>
+  <si>
+    <t>Bawal na kasuotan</t>
+  </si>
+  <si>
+    <t>Hindi ayon sa dress code</t>
+  </si>
+  <si>
+    <t>Casual lang ang suot</t>
+  </si>
+  <si>
+    <t>Labag sa uniform policy</t>
+  </si>
+  <si>
+    <t>Di angkop na pananamit</t>
+  </si>
+  <si>
+    <t>Cellphone use during class</t>
+  </si>
+  <si>
+    <t>Unauthorized cellphone use</t>
+  </si>
+  <si>
+    <t>No phone policy violation</t>
+  </si>
+  <si>
+    <t>Using phone in class</t>
+  </si>
+  <si>
+    <t>Prohibited phone usage</t>
+  </si>
+  <si>
+    <t>Cellphone seen in lecture</t>
+  </si>
+  <si>
+    <t>Mobile phone distraction</t>
+  </si>
+  <si>
+    <t>Hindi awtorisadong paggamit ng cellphone</t>
+  </si>
+  <si>
+    <t>Paggamit ng cellphone sa klase</t>
+  </si>
+  <si>
+    <t>Paglabag sa no phone rule</t>
+  </si>
+  <si>
+    <t>Cellphone used without permission</t>
+  </si>
+  <si>
+    <t>Improper phone use</t>
+  </si>
+  <si>
+    <t>Phone usage violation</t>
+  </si>
+  <si>
+    <t>Bawal na paggamit ng cellphone</t>
+  </si>
+  <si>
+    <t>Cellphone confiscation case</t>
+  </si>
+  <si>
+    <t>Present Fake ID</t>
+  </si>
+  <si>
+    <t>Forgot the ID</t>
+  </si>
+  <si>
+    <t>Pambu-bully sa kaklase</t>
+  </si>
+  <si>
+    <t>Pangha-harass sa kaklase</t>
+  </si>
+  <si>
+    <t>Walang suot na ID</t>
   </si>
 </sst>
 </file>
@@ -2436,7 +2673,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C951"/>
+  <dimension ref="A1:C1030"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="157.88671875" customWidth="1"/>
@@ -12905,6 +13142,875 @@
         <v>380</v>
       </c>
     </row>
+    <row r="952" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A952" t="s">
+        <v>681</v>
+      </c>
+      <c r="B952" t="s">
+        <v>370</v>
+      </c>
+      <c r="C952" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="953" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A953" t="s">
+        <v>682</v>
+      </c>
+      <c r="B953" t="s">
+        <v>370</v>
+      </c>
+      <c r="C953" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="954" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A954" t="s">
+        <v>759</v>
+      </c>
+      <c r="B954" t="s">
+        <v>375</v>
+      </c>
+      <c r="C954" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="955" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A955" t="s">
+        <v>683</v>
+      </c>
+      <c r="B955" t="s">
+        <v>371</v>
+      </c>
+      <c r="C955" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="956" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A956" t="s">
+        <v>684</v>
+      </c>
+      <c r="B956" t="s">
+        <v>371</v>
+      </c>
+      <c r="C956" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="957" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A957" t="s">
+        <v>685</v>
+      </c>
+      <c r="B957" t="s">
+        <v>371</v>
+      </c>
+      <c r="C957" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="958" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A958" t="s">
+        <v>686</v>
+      </c>
+      <c r="B958" t="s">
+        <v>371</v>
+      </c>
+      <c r="C958" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="959" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A959" t="s">
+        <v>687</v>
+      </c>
+      <c r="B959" t="s">
+        <v>371</v>
+      </c>
+      <c r="C959" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="960" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A960" t="s">
+        <v>688</v>
+      </c>
+      <c r="B960" t="s">
+        <v>371</v>
+      </c>
+      <c r="C960" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="961" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A961" t="s">
+        <v>689</v>
+      </c>
+      <c r="B961" t="s">
+        <v>371</v>
+      </c>
+      <c r="C961" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="962" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A962" t="s">
+        <v>757</v>
+      </c>
+      <c r="B962" t="s">
+        <v>371</v>
+      </c>
+      <c r="C962" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="963" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A963" t="s">
+        <v>758</v>
+      </c>
+      <c r="B963" t="s">
+        <v>371</v>
+      </c>
+      <c r="C963" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="964" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A964" t="s">
+        <v>690</v>
+      </c>
+      <c r="B964" t="s">
+        <v>371</v>
+      </c>
+      <c r="C964" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="965" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A965" t="s">
+        <v>691</v>
+      </c>
+      <c r="B965" t="s">
+        <v>370</v>
+      </c>
+      <c r="C965" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="966" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A966" t="s">
+        <v>692</v>
+      </c>
+      <c r="B966" t="s">
+        <v>370</v>
+      </c>
+      <c r="C966" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="967" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A967" t="s">
+        <v>693</v>
+      </c>
+      <c r="B967" t="s">
+        <v>375</v>
+      </c>
+      <c r="C967" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="968" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A968" t="s">
+        <v>694</v>
+      </c>
+      <c r="B968" t="s">
+        <v>375</v>
+      </c>
+      <c r="C968" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="969" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A969" t="s">
+        <v>695</v>
+      </c>
+      <c r="B969" t="s">
+        <v>373</v>
+      </c>
+      <c r="C969" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="970" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A970" t="s">
+        <v>696</v>
+      </c>
+      <c r="B970" t="s">
+        <v>373</v>
+      </c>
+      <c r="C970" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="971" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A971" t="s">
+        <v>697</v>
+      </c>
+      <c r="B971" t="s">
+        <v>371</v>
+      </c>
+      <c r="C971" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="972" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A972" t="s">
+        <v>698</v>
+      </c>
+      <c r="B972" t="s">
+        <v>371</v>
+      </c>
+      <c r="C972" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="973" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A973" t="s">
+        <v>699</v>
+      </c>
+      <c r="B973" t="s">
+        <v>371</v>
+      </c>
+      <c r="C973" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="974" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A974" t="s">
+        <v>700</v>
+      </c>
+      <c r="B974" t="s">
+        <v>371</v>
+      </c>
+      <c r="C974" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="975" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A975" t="s">
+        <v>701</v>
+      </c>
+      <c r="B975" t="s">
+        <v>371</v>
+      </c>
+      <c r="C975" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="976" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A976" t="s">
+        <v>702</v>
+      </c>
+      <c r="B976" t="s">
+        <v>371</v>
+      </c>
+      <c r="C976" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="977" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A977" t="s">
+        <v>703</v>
+      </c>
+      <c r="B977" t="s">
+        <v>371</v>
+      </c>
+      <c r="C977" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="978" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A978" t="s">
+        <v>704</v>
+      </c>
+      <c r="B978" t="s">
+        <v>371</v>
+      </c>
+      <c r="C978" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="979" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A979" t="s">
+        <v>705</v>
+      </c>
+      <c r="B979" t="s">
+        <v>371</v>
+      </c>
+      <c r="C979" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="980" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A980" t="s">
+        <v>706</v>
+      </c>
+      <c r="B980" t="s">
+        <v>371</v>
+      </c>
+      <c r="C980" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="981" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A981" t="s">
+        <v>707</v>
+      </c>
+      <c r="B981" t="s">
+        <v>371</v>
+      </c>
+      <c r="C981" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="982" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A982" t="s">
+        <v>708</v>
+      </c>
+      <c r="B982" t="s">
+        <v>371</v>
+      </c>
+      <c r="C982" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="983" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A983" t="s">
+        <v>709</v>
+      </c>
+      <c r="B983" t="s">
+        <v>371</v>
+      </c>
+      <c r="C983" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="984" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A984" t="s">
+        <v>710</v>
+      </c>
+      <c r="B984" t="s">
+        <v>371</v>
+      </c>
+      <c r="C984" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="985" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A985" t="s">
+        <v>711</v>
+      </c>
+      <c r="B985" t="s">
+        <v>371</v>
+      </c>
+      <c r="C985" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="986" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A986" t="s">
+        <v>712</v>
+      </c>
+      <c r="B986" t="s">
+        <v>371</v>
+      </c>
+      <c r="C986" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="987" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A987" t="s">
+        <v>755</v>
+      </c>
+      <c r="B987" t="s">
+        <v>375</v>
+      </c>
+      <c r="C987" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="988" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A988" t="s">
+        <v>713</v>
+      </c>
+      <c r="B988" t="s">
+        <v>375</v>
+      </c>
+      <c r="C988" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="989" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A989" t="s">
+        <v>714</v>
+      </c>
+      <c r="B989" t="s">
+        <v>375</v>
+      </c>
+      <c r="C989" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="990" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A990" t="s">
+        <v>756</v>
+      </c>
+      <c r="B990" t="s">
+        <v>375</v>
+      </c>
+      <c r="C990" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="991" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A991" t="s">
+        <v>715</v>
+      </c>
+      <c r="B991" t="s">
+        <v>375</v>
+      </c>
+      <c r="C991" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="992" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A992" t="s">
+        <v>717</v>
+      </c>
+      <c r="B992" t="s">
+        <v>375</v>
+      </c>
+      <c r="C992" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="993" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A993" t="s">
+        <v>716</v>
+      </c>
+      <c r="B993" t="s">
+        <v>375</v>
+      </c>
+      <c r="C993" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="994" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A994" t="s">
+        <v>718</v>
+      </c>
+      <c r="B994" t="s">
+        <v>375</v>
+      </c>
+      <c r="C994" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="995" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A995" t="s">
+        <v>719</v>
+      </c>
+      <c r="B995" t="s">
+        <v>375</v>
+      </c>
+      <c r="C995" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="996" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A996" t="s">
+        <v>720</v>
+      </c>
+      <c r="B996" t="s">
+        <v>375</v>
+      </c>
+      <c r="C996" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="997" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A997" t="s">
+        <v>721</v>
+      </c>
+      <c r="B997" t="s">
+        <v>375</v>
+      </c>
+      <c r="C997" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="998" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A998" t="s">
+        <v>722</v>
+      </c>
+      <c r="B998" t="s">
+        <v>375</v>
+      </c>
+      <c r="C998" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="999" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A999" t="s">
+        <v>723</v>
+      </c>
+      <c r="B999" t="s">
+        <v>375</v>
+      </c>
+      <c r="C999" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1000" t="s">
+        <v>724</v>
+      </c>
+      <c r="B1000" t="s">
+        <v>375</v>
+      </c>
+      <c r="C1000" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1001" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1001" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1001" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1002" t="s">
+        <v>726</v>
+      </c>
+      <c r="B1002" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1002" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1003" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1003" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1003" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1004" t="s">
+        <v>727</v>
+      </c>
+      <c r="B1004" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1004" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1005" t="s">
+        <v>729</v>
+      </c>
+      <c r="B1005" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1005" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1006" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1006" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1006" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1007" t="s">
+        <v>731</v>
+      </c>
+      <c r="B1007" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1007" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1008" t="s">
+        <v>732</v>
+      </c>
+      <c r="B1008" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1008" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1009" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1009" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1009" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1010" t="s">
+        <v>734</v>
+      </c>
+      <c r="B1010" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1010" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1011" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1011" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1011" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1012" t="s">
+        <v>736</v>
+      </c>
+      <c r="B1012" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1012" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1013" t="s">
+        <v>737</v>
+      </c>
+      <c r="B1013" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1013" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1014" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1014" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1014" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1015" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1015" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1015" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1016" t="s">
+        <v>740</v>
+      </c>
+      <c r="B1016" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1016" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1017" t="s">
+        <v>741</v>
+      </c>
+      <c r="B1017" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1017" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1018" t="s">
+        <v>742</v>
+      </c>
+      <c r="B1018" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1018" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1019" t="s">
+        <v>743</v>
+      </c>
+      <c r="B1019" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1019" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1020" t="s">
+        <v>744</v>
+      </c>
+      <c r="B1020" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1020" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1021" t="s">
+        <v>745</v>
+      </c>
+      <c r="B1021" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1021" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1022" t="s">
+        <v>746</v>
+      </c>
+      <c r="B1022" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1022" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1023" t="s">
+        <v>747</v>
+      </c>
+      <c r="B1023" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1023" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1024" t="s">
+        <v>748</v>
+      </c>
+      <c r="B1024" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1024" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1025" t="s">
+        <v>749</v>
+      </c>
+      <c r="B1025" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1025" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1026" t="s">
+        <v>750</v>
+      </c>
+      <c r="B1026" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1026" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1027" t="s">
+        <v>751</v>
+      </c>
+      <c r="B1027" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1027" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1028" t="s">
+        <v>752</v>
+      </c>
+      <c r="B1028" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1028" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1029" t="s">
+        <v>753</v>
+      </c>
+      <c r="B1029" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1029" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1030" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1030" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1030" t="s">
+        <v>380</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
